--- a/vlearn-app/public/quiz_excel/Day_10_Data Pipeline _ Observability/Day_10_Phan_03_21_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_10_Data Pipeline _ Observability/Day_10_Phan_03_21_Cau.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -638,7 +638,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Age bắt đầu ở source/effective time.</t>
+          <t>Độ tuổi của dữ liệu (data age) mà consumer quan sát được theo watermark: Tính từ mốc thời gian watermark an toàn (14:40) đến thời điểm hiện tại của hệ thống (15:10): 15:10 - 14:40 = 30 phút.</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -735,7 +735,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal có thể phản ánh parser làm rỗng/cắt/đổi language.</t>
+          <t>Khi số lượng dòng vẫn ổn định nhưng chất lượng câu trả lời bị suy giảm sau khi cập nhật bộ phân tích cú pháp (parser), các tín hiệu hữu ích để phát hiện sự cố dữ liệu gồm: (a) Tỷ lệ giá trị null theo từng trường dữ liệu; (b) Phân phối độ dài văn bản (text-length distribution) phát hiện hiện tượng bị cắt cụt; (c) Tỷ lệ phối hợp ngôn ngữ (language mix) phát hiện lỗi dịch/nhầm locale; (d) Số lượng giá trị phân biệt và độ hỗn loạn thông tin (cardinality/entropy) phát hiện lỗi trùng lặp/giảm đa dạng.</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o5 → o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -832,7 +832,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu ở thứ agent nhìn thấy rồi lần producer của từng artifact.</t>
+          <t>Trình tự truy vết nguồn gốc dữ liệu ngược dòng (backwards data lineage) từ kết quả phục vụ agent về nguồn dữ liệu gốc: 1. Retrieved chunk mà agent trực tiếp quan sát thấy trong context (o5) -&gt; 2. Active index snapshot đang phục vụ truy vấn tại thời điểm đó (o2) -&gt; 3. Bản ghi chuẩn hóa (canonical record) trong kho lưu trữ (o4) -&gt; 4. Tác vụ và artifact chuyển đổi (transform run/artifact) tạo ra bản ghi đó (o1) -&gt; 5. Định danh và phiên bản dữ liệu nguồn ban đầu (source identity/version) (o3).</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -884,7 +884,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi khi breach thì ai biết, ai làm gì và learner thấy gì.</t>
+          <t>Một thỏa thuận mức dịch vụ về độ tươi mới dữ liệu (freshness SLA) có tính hành động cao bắt buộc phải có: (a) Thời điểm phát sinh sự kiện kinh doanh tại nguồn để bắt đầu tính thời gian; (b) Ranh giới xuất bản dữ liệu phục vụ agent để kết thúc tính thời gian; (c) Ngưỡng thời gian và quy trình cảnh báo/leo thang khi vi phạm; (d) Người chịu trách nhiệm cụ thể và quy định hành vi xử lý khi dữ liệu bị cũ/quá hạn (stale-data policy).</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1128,7 +1128,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét lúc source trễ, task giữa DAG fail và cần chạy lại một date range.</t>
+          <t>Để vận hành một pipeline dữ liệu tin cậy trong môi trường sản xuất, ngoài lịch chạy cron cần bổ sung các yêu cầu bắt buộc: (a) Đồ thị phụ thuộc dữ liệu và điều kiện sẵn sàng của dữ liệu nguồn (dependency graph / data sensors); (b) Chính sách thử lại riêng cho từng tác vụ kèm giới hạn tối đa; (c) Cơ chế cảnh báo vi phạm SLA, người sở hữu phụ trách và khả năng hiển thị trạng thái thực thi; (d) Các tham số chạy bù dữ liệu có chặn giới hạn (bounded backfill) và quản lý dấu vết dữ liệu (lineage).</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o1 → o3 → o4 → o5</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không write trực tiếp vào alias đang serve.</t>
+          <t>Quy trình phát hành chỉ mục vector nguyên tử (atomic vector index publish) bảo đảm tính sẵn sàng: 1. Xây dựng bộ sưu tập staging độc lập (build staging collection) (o2) -&gt; 2. Xác minh số lượng bản ghi, schema, mẫu dữ liệu và manifest trên staging (o1) -&gt; 3. Chuyển đổi alias phục vụ sang bộ sưu tập staging một cách nguyên tử (switch serving alias atomically) (o3) -&gt; 4. Duy trì snapshot phiên bản phục vụ trước đó trong khoảng thời gian an toàn (o4) -&gt; 5. Rollback alias về snapshot cũ nếu các phép kiểm sau phát hành thất bại (o5).</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o5 → o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định incident trước, rồi dùng signal rộng/rẻ trước targeted lineage.</t>
+          <t>Trình tự phân loại và xử lý sự cố dữ liệu (data incident triage) tối ưu chi phí và thời gian: 1. Ghi nhận triệu chứng sự cố, vi phạm SLA, phạm vi ảnh hưởng và giả thuyết ban đầu (o5) -&gt; 2. Kiểm tra độ tươi mới và mốc chạy thành công gần nhất (freshness/last success) (o2) -&gt; 3. Kiểm tra khối lượng dữ liệu và tỷ lệ lỗi theo từng giai đoạn đường ống (volume/stage errors) (o4) -&gt; 4. Kiểm tra các thay đổi về cấu trúc schema hoặc hợp đồng dữ liệu gần đây (o1) -&gt; 5. Truy vết ngược dòng lineage chi tiết về tận nguồn dữ liệu và người sở hữu phụ trách (o3).</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -1419,7 +1419,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Verify từ source tới bề mặt agent.</t>
+          <t>Bằng chứng kỹ thuật đầy đủ và thuyết phục để chính thức đóng một sự cố dữ liệu (data incident) bao gồm: (a) Bản ghi nguồn và bản ghi chuẩn hóa đã được xác minh đúng kèm đầy đủ lineage; (b) Các tín hiệu kiểm tra chất lượng dữ liệu liên quan đã vượt qua thành công; (c) Snapshot đang hoạt động ở tầng phục vụ mang đúng ID phiên bản đã khắc phục; (d) Truy vấn thực tế của người dùng ban đầu được chạy lại và trả về câu trả lời cùng trích dẫn nguồn hoàn toàn chính xác.</t>
         </is>
       </c>
     </row>
